--- a/第7回_Softmax_Generation/excel_softmax_generation_demo.xlsx
+++ b/第7回_Softmax_Generation/excel_softmax_generation_demo.xlsx
@@ -99,7 +99,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -121,11 +121,17 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <right/>
+      <bottom style="thin">
+        <color rgb="00D8DEE9"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -157,6 +163,9 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -535,7 +544,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="12" t="inlineStr">
         <is>
           <t>Excelで体験する言語モデルのしくみ 第7回 Softmaxと生成のばらつき</t>
         </is>
@@ -660,7 +669,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="12" t="inlineStr">
         <is>
           <t>12_TROUBLE: よくある確認点</t>
         </is>
@@ -685,7 +694,7 @@
           <t>よくある確認点</t>
         </is>
       </c>
-      <c r="B4" s="3" t="n"/>
+      <c r="B4" s="2" t="n"/>
     </row>
     <row r="5" ht="24" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
@@ -774,7 +783,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="12" t="inlineStr">
         <is>
           <t>13_SERIES_ROADMAP</t>
         </is>
@@ -801,8 +810,8 @@
           <t>全10回ロードマップ</t>
         </is>
       </c>
-      <c r="B4" s="3" t="n"/>
-      <c r="C4" s="3" t="n"/>
+      <c r="B4" s="2" t="n"/>
+      <c r="C4" s="2" t="n"/>
     </row>
     <row r="5" ht="24" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
@@ -1022,7 +1031,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="12" t="inlineStr">
         <is>
           <t>01_INPUT: Softmaxへ渡す候補tokenと設定</t>
         </is>
@@ -1055,15 +1064,15 @@
           <t>第6回のBlock Output後に語彙ごとのlogitが得られたと仮定し、Softmaxと選択方法だけを小さく確認します。</t>
         </is>
       </c>
-      <c r="B3" s="3" t="n"/>
-      <c r="C3" s="3" t="n"/>
-      <c r="D3" s="3" t="n"/>
-      <c r="E3" s="3" t="n"/>
-      <c r="F3" s="3" t="n"/>
-      <c r="G3" s="3" t="n"/>
-      <c r="H3" s="3" t="n"/>
-      <c r="I3" s="3" t="n"/>
-      <c r="J3" s="3" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
     </row>
     <row r="4" ht="24" customHeight="1">
       <c r="A4" s="3" t="n"/>
@@ -1083,7 +1092,7 @@
           <t>文脈token</t>
         </is>
       </c>
-      <c r="B5" s="3" t="n"/>
+      <c r="B5" s="2" t="n"/>
       <c r="C5" s="3" t="n"/>
       <c r="D5" s="3" t="n"/>
       <c r="E5" s="4" t="inlineStr">
@@ -1091,7 +1100,7 @@
           <t>候補tokenとlogit</t>
         </is>
       </c>
-      <c r="F5" s="3" t="n"/>
+      <c r="F5" s="2" t="n"/>
       <c r="G5" s="3" t="n"/>
       <c r="H5" s="3" t="n"/>
       <c r="I5" s="3" t="n"/>
@@ -1275,8 +1284,8 @@
           <t>生成設定</t>
         </is>
       </c>
-      <c r="B14" s="3" t="n"/>
-      <c r="C14" s="3" t="n"/>
+      <c r="B14" s="2" t="n"/>
+      <c r="C14" s="2" t="n"/>
       <c r="D14" s="3" t="n"/>
       <c r="E14" s="3" t="n"/>
       <c r="F14" s="3" t="n"/>
@@ -1409,7 +1418,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="12" t="inlineStr">
         <is>
           <t>02_LOGITS_SOFTMAX: logitを確率へ変換する</t>
         </is>
@@ -1438,13 +1447,13 @@
           <t>logitは確率そのものではありません。Softmaxで合計1の確率に変換してから候補を選びます。</t>
         </is>
       </c>
-      <c r="B3" s="3" t="n"/>
-      <c r="C3" s="3" t="n"/>
-      <c r="D3" s="3" t="n"/>
-      <c r="E3" s="3" t="n"/>
-      <c r="F3" s="3" t="n"/>
-      <c r="G3" s="3" t="n"/>
-      <c r="H3" s="3" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
     </row>
     <row r="4" ht="24" customHeight="1">
       <c r="A4" s="3" t="n"/>
@@ -1462,10 +1471,10 @@
           <t>temperature=1.0 の確率表</t>
         </is>
       </c>
-      <c r="B5" s="3" t="n"/>
-      <c r="C5" s="3" t="n"/>
-      <c r="D5" s="3" t="n"/>
-      <c r="E5" s="3" t="n"/>
+      <c r="B5" s="2" t="n"/>
+      <c r="C5" s="2" t="n"/>
+      <c r="D5" s="2" t="n"/>
+      <c r="E5" s="2" t="n"/>
       <c r="F5" s="3" t="n"/>
       <c r="G5" s="3" t="n"/>
       <c r="H5" s="3" t="n"/>
@@ -1662,7 +1671,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="12" t="inlineStr">
         <is>
           <t>03_TEMPERATURE: temperatureで確率の尖り方が変わる</t>
         </is>
@@ -1691,13 +1700,13 @@
           <t>temperatureを下げると上位候補に寄り、上げると候補間の差がなだらかになります。</t>
         </is>
       </c>
-      <c r="B3" s="3" t="n"/>
-      <c r="C3" s="3" t="n"/>
-      <c r="D3" s="3" t="n"/>
-      <c r="E3" s="3" t="n"/>
-      <c r="F3" s="3" t="n"/>
-      <c r="G3" s="3" t="n"/>
-      <c r="H3" s="3" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
     </row>
     <row r="4" ht="24" customHeight="1">
       <c r="A4" s="3" t="n"/>
@@ -1715,11 +1724,11 @@
           <t>temperature比較</t>
         </is>
       </c>
-      <c r="B5" s="3" t="n"/>
-      <c r="C5" s="3" t="n"/>
-      <c r="D5" s="3" t="n"/>
-      <c r="E5" s="3" t="n"/>
-      <c r="F5" s="3" t="n"/>
+      <c r="B5" s="2" t="n"/>
+      <c r="C5" s="2" t="n"/>
+      <c r="D5" s="2" t="n"/>
+      <c r="E5" s="2" t="n"/>
+      <c r="F5" s="2" t="n"/>
       <c r="G5" s="3" t="n"/>
       <c r="H5" s="3" t="n"/>
     </row>
@@ -2220,7 +2229,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="12" t="inlineStr">
         <is>
           <t>04_SELECTION_METHODS: 次tokenの選び方</t>
         </is>
@@ -2251,14 +2260,14 @@
           <t>確率表が同じでも、greedy、sampling、top-kでは選ばれ方が変わります。</t>
         </is>
       </c>
-      <c r="B3" s="3" t="n"/>
-      <c r="C3" s="3" t="n"/>
-      <c r="D3" s="3" t="n"/>
-      <c r="E3" s="3" t="n"/>
-      <c r="F3" s="3" t="n"/>
-      <c r="G3" s="3" t="n"/>
-      <c r="H3" s="3" t="n"/>
-      <c r="I3" s="3" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
     </row>
     <row r="4" ht="24" customHeight="1">
       <c r="A4" s="3" t="n"/>
@@ -2277,8 +2286,8 @@
           <t>選択方法</t>
         </is>
       </c>
-      <c r="B5" s="3" t="n"/>
-      <c r="C5" s="3" t="n"/>
+      <c r="B5" s="2" t="n"/>
+      <c r="C5" s="2" t="n"/>
       <c r="D5" s="3" t="n"/>
       <c r="E5" s="3" t="n"/>
       <c r="F5" s="3" t="n"/>
@@ -2395,10 +2404,10 @@
           <t>top-kで残す候補</t>
         </is>
       </c>
-      <c r="B11" s="3" t="n"/>
-      <c r="C11" s="3" t="n"/>
-      <c r="D11" s="3" t="n"/>
-      <c r="E11" s="3" t="n"/>
+      <c r="B11" s="2" t="n"/>
+      <c r="C11" s="2" t="n"/>
+      <c r="D11" s="2" t="n"/>
+      <c r="E11" s="2" t="n"/>
       <c r="F11" s="3" t="n"/>
       <c r="G11" s="3" t="n"/>
       <c r="H11" s="3" t="n"/>
@@ -2535,7 +2544,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="12" t="inlineStr">
         <is>
           <t>05_SAMPLING_RUNS: seed違いで生成がばらつく</t>
         </is>
@@ -2564,13 +2573,13 @@
           <t>samplingでは確率に沿って選ぶため、最大確率以外のtokenが選ばれることがあります。</t>
         </is>
       </c>
-      <c r="B3" s="3" t="n"/>
-      <c r="C3" s="3" t="n"/>
-      <c r="D3" s="3" t="n"/>
-      <c r="E3" s="3" t="n"/>
-      <c r="F3" s="3" t="n"/>
-      <c r="G3" s="3" t="n"/>
-      <c r="H3" s="3" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
     </row>
     <row r="4" ht="24" customHeight="1">
       <c r="A4" s="3" t="n"/>
@@ -2588,9 +2597,9 @@
           <t>sampling結果</t>
         </is>
       </c>
-      <c r="B5" s="3" t="n"/>
-      <c r="C5" s="3" t="n"/>
-      <c r="D5" s="3" t="n"/>
+      <c r="B5" s="2" t="n"/>
+      <c r="C5" s="2" t="n"/>
+      <c r="D5" s="2" t="n"/>
       <c r="E5" s="3" t="n"/>
       <c r="F5" s="3" t="n"/>
       <c r="G5" s="3" t="n"/>
@@ -2760,7 +2769,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="12" t="inlineStr">
         <is>
           <t>06_GENERATION_FLOW: 生成の流れ</t>
         </is>
@@ -2787,8 +2796,8 @@
           <t>生成フロー</t>
         </is>
       </c>
-      <c r="B4" s="3" t="n"/>
-      <c r="C4" s="3" t="n"/>
+      <c r="B4" s="2" t="n"/>
+      <c r="C4" s="2" t="n"/>
     </row>
     <row r="5" ht="24" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
@@ -2919,7 +2928,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="12" t="inlineStr">
         <is>
           <t>10_RUN_PYTHON: Python in Excel 実行手順</t>
         </is>
@@ -2944,7 +2953,7 @@
           <t>実行手順</t>
         </is>
       </c>
-      <c r="B4" s="3" t="n"/>
+      <c r="B4" s="2" t="n"/>
     </row>
     <row r="5" ht="24" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
@@ -3033,7 +3042,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F88"/>
+  <dimension ref="A1:A95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="135" customWidth="1" min="1" max="1"/>
@@ -3045,577 +3054,615 @@
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>11_PYTHON_CODE: Python in Excelへ貼り付けるコード</t>
         </is>
       </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="2" t="n"/>
-      <c r="D1" s="2" t="n"/>
-      <c r="E1" s="2" t="n"/>
-      <c r="F1" s="2" t="n"/>
     </row>
     <row r="2" ht="24" customHeight="1">
-      <c r="A2" s="3" t="n"/>
-    </row>
-    <row r="3" ht="24" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>外部 .py ファイルと同じ内容です。Excelの入力表を xl(...) で参照します。</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="24" customHeight="1"/>
+    <row r="4" ht="24" customHeight="1">
+      <c r="A4" t="inlineStr">
         <is>
           <t>import pandas as pd</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="24" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
+    <row r="5" ht="24" customHeight="1">
+      <c r="A5" t="inlineStr">
         <is>
           <t>import numpy as np</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="24" customHeight="1">
-      <c r="A5" s="3" t="inlineStr"/>
-    </row>
     <row r="6" ht="24" customHeight="1">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>context_tokens = ["今日", "猫", "ごはん", "食べる"]</t>
-        </is>
-      </c>
+      <c r="A6" t="inlineStr"/>
     </row>
     <row r="7" ht="24" customHeight="1">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>vocab = ["です", "ました", "ね", "よ", "犬", "走る"]</t>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>context_source_df = xl("'01_INPUT'!A6:B12", headers=True).dropna(how="all")</t>
         </is>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>logits = np.array([2.2, 1.5, 0.9, 0.4, -0.2, -0.8])</t>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>candidate_source_df = xl("'01_INPUT'!E6:F12", headers=True).dropna(how="all")</t>
         </is>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>temperatures = [0.7, 1.0, 1.5]</t>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>settings_source_df = xl("'01_INPUT'!A15:C18", headers=True).dropna(how="all")</t>
         </is>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>top_k = 3</t>
-        </is>
-      </c>
+      <c r="A10" t="inlineStr"/>
     </row>
     <row r="11" ht="24" customHeight="1">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>seeds = [11, 22, 33, 44, 55]</t>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>context_tokens = context_source_df["token"].dropna().astype(str).tolist()</t>
         </is>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1">
-      <c r="A12" s="3" t="inlineStr"/>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>vocab = candidate_source_df["candidate_token"].astype(str).tolist()</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="24" customHeight="1">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>logits = candidate_source_df["logit"].astype(float).to_numpy()</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="24" customHeight="1">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>settings = dict(zip(settings_source_df["parameter"].astype(str), settings_source_df["value"]))</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="24" customHeight="1">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>temperature = float(settings.get("temperature", 1.0))</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="24" customHeight="1">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>temperatures = [0.7, temperature, 1.5]</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="24" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>top_k = int(float(settings.get("top_k", 3)))</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="24" customHeight="1">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>seeds = [int(s.strip()) for s in str(settings.get("seed", "11, 22, 33, 44, 55")).split(",") if s.strip()]</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="24" customHeight="1">
+      <c r="A19" t="inlineStr"/>
+    </row>
+    <row r="20" ht="24" customHeight="1">
+      <c r="A20" t="inlineStr">
         <is>
           <t>def softmax(values, temperature=1.0):</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="24" customHeight="1">
-      <c r="A14" s="3" t="inlineStr">
+    <row r="21" ht="24" customHeight="1">
+      <c r="A21" t="inlineStr">
         <is>
           <t xml:space="preserve">    scaled = values / temperature</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="24" customHeight="1">
-      <c r="A15" s="3" t="inlineStr">
+    <row r="22" ht="24" customHeight="1">
+      <c r="A22" t="inlineStr">
         <is>
           <t xml:space="preserve">    shifted = scaled - scaled.max()</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="24" customHeight="1">
-      <c r="A16" s="3" t="inlineStr">
+    <row r="23" ht="24" customHeight="1">
+      <c r="A23" t="inlineStr">
         <is>
           <t xml:space="preserve">    exps = np.exp(shifted)</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="24" customHeight="1">
-      <c r="A17" s="3" t="inlineStr">
+    <row r="24" ht="24" customHeight="1">
+      <c r="A24" t="inlineStr">
         <is>
           <t xml:space="preserve">    return exps / exps.sum()</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="24" customHeight="1">
-      <c r="A18" s="3" t="inlineStr"/>
-    </row>
-    <row r="19" ht="24" customHeight="1">
-      <c r="A19" s="3" t="inlineStr">
+    <row r="25" ht="24" customHeight="1">
+      <c r="A25" t="inlineStr"/>
+    </row>
+    <row r="26" ht="24" customHeight="1">
+      <c r="A26" t="inlineStr">
         <is>
           <t>def sample_from_probs(tokens, probabilities, seed):</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="24" customHeight="1">
-      <c r="A20" s="3" t="inlineStr">
+    <row r="27" ht="24" customHeight="1">
+      <c r="A27" t="inlineStr">
         <is>
           <t xml:space="preserve">    rng = np.random.default_rng(seed)</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="24" customHeight="1">
-      <c r="A21" s="3" t="inlineStr">
+    <row r="28" ht="24" customHeight="1">
+      <c r="A28" t="inlineStr">
         <is>
           <t xml:space="preserve">    r = float(rng.random())</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="24" customHeight="1">
-      <c r="A22" s="3" t="inlineStr">
+    <row r="29" ht="24" customHeight="1">
+      <c r="A29" t="inlineStr">
         <is>
           <t xml:space="preserve">    cumulative = np.cumsum(probabilities)</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="24" customHeight="1">
-      <c r="A23" s="3" t="inlineStr">
+    <row r="30" ht="24" customHeight="1">
+      <c r="A30" t="inlineStr">
         <is>
           <t xml:space="preserve">    picked_index = int(np.searchsorted(cumulative, r, side="right"))</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="24" customHeight="1">
-      <c r="A24" s="3" t="inlineStr">
+    <row r="31" ht="24" customHeight="1">
+      <c r="A31" t="inlineStr">
         <is>
           <t xml:space="preserve">    picked_index = min(picked_index, len(tokens) - 1)</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="24" customHeight="1">
-      <c r="A25" s="3" t="inlineStr">
+    <row r="32" ht="24" customHeight="1">
+      <c r="A32" t="inlineStr">
         <is>
           <t xml:space="preserve">    return tokens[picked_index], r</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="24" customHeight="1">
-      <c r="A26" s="3" t="inlineStr"/>
-    </row>
-    <row r="27" ht="24" customHeight="1">
-      <c r="A27" s="3" t="inlineStr">
+    <row r="33" ht="24" customHeight="1">
+      <c r="A33" t="inlineStr"/>
+    </row>
+    <row r="34" ht="24" customHeight="1">
+      <c r="A34" t="inlineStr">
         <is>
           <t>score_rows = []</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="24" customHeight="1">
-      <c r="A28" s="3" t="inlineStr">
+    <row r="35" ht="24" customHeight="1">
+      <c r="A35" t="inlineStr">
         <is>
           <t>temperature_rows = []</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="24" customHeight="1">
-      <c r="A29" s="3" t="inlineStr">
+    <row r="36" ht="24" customHeight="1">
+      <c r="A36" t="inlineStr">
         <is>
           <t>for temp in temperatures:</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="24" customHeight="1">
-      <c r="A30" s="3" t="inlineStr">
+    <row r="37" ht="24" customHeight="1">
+      <c r="A37" t="inlineStr">
         <is>
           <t xml:space="preserve">    probs = softmax(logits, temp)</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="24" customHeight="1">
-      <c r="A31" s="3" t="inlineStr">
+    <row r="38" ht="24" customHeight="1">
+      <c r="A38" t="inlineStr">
         <is>
           <t xml:space="preserve">    order = np.argsort(-probs)</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="24" customHeight="1">
-      <c r="A32" s="3" t="inlineStr">
+    <row r="39" ht="24" customHeight="1">
+      <c r="A39" t="inlineStr">
         <is>
           <t xml:space="preserve">    for rank, idx in enumerate(order, start=1):</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="24" customHeight="1">
-      <c r="A33" s="3" t="inlineStr">
+    <row r="40" ht="24" customHeight="1">
+      <c r="A40" t="inlineStr">
         <is>
           <t xml:space="preserve">        row = {</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="24" customHeight="1">
-      <c r="A34" s="3" t="inlineStr">
+    <row r="41" ht="24" customHeight="1">
+      <c r="A41" t="inlineStr">
         <is>
           <t xml:space="preserve">            "temperature": temp,</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="24" customHeight="1">
-      <c r="A35" s="3" t="inlineStr">
+    <row r="42" ht="24" customHeight="1">
+      <c r="A42" t="inlineStr">
         <is>
           <t xml:space="preserve">            "rank": rank,</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="24" customHeight="1">
-      <c r="A36" s="3" t="inlineStr">
+    <row r="43" ht="24" customHeight="1">
+      <c r="A43" t="inlineStr">
         <is>
           <t xml:space="preserve">            "candidate_token": vocab[idx],</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="24" customHeight="1">
-      <c r="A37" s="3" t="inlineStr">
+    <row r="44" ht="24" customHeight="1">
+      <c r="A44" t="inlineStr">
         <is>
           <t xml:space="preserve">            "logit": round(float(logits[idx]), 4),</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="24" customHeight="1">
-      <c r="A38" s="3" t="inlineStr">
+    <row r="45" ht="24" customHeight="1">
+      <c r="A45" t="inlineStr">
         <is>
           <t xml:space="preserve">            "scaled_logit": round(float(logits[idx] / temp), 4),</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="24" customHeight="1">
-      <c r="A39" s="3" t="inlineStr">
+    <row r="46" ht="24" customHeight="1">
+      <c r="A46" t="inlineStr">
         <is>
           <t xml:space="preserve">            "probability": round(float(probs[idx]), 4),</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="24" customHeight="1">
-      <c r="A40" s="3" t="inlineStr">
+    <row r="47" ht="24" customHeight="1">
+      <c r="A47" t="inlineStr">
         <is>
           <t xml:space="preserve">        }</t>
         </is>
       </c>
     </row>
-    <row r="41" ht="24" customHeight="1">
-      <c r="A41" s="3" t="inlineStr">
+    <row r="48" ht="24" customHeight="1">
+      <c r="A48" t="inlineStr">
         <is>
           <t xml:space="preserve">        temperature_rows.append(row)</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="24" customHeight="1">
-      <c r="A42" s="3" t="inlineStr">
+    <row r="49" ht="24" customHeight="1">
+      <c r="A49" t="inlineStr">
         <is>
           <t xml:space="preserve">        if temp == 1.0:</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="24" customHeight="1">
-      <c r="A43" s="3" t="inlineStr">
+    <row r="50" ht="24" customHeight="1">
+      <c r="A50" t="inlineStr">
         <is>
           <t xml:space="preserve">            score_rows.append({k: row[k] for k in ["rank", "candidate_token", "logit", "scaled_logit", "probability"]})</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="24" customHeight="1">
-      <c r="A44" s="3" t="inlineStr"/>
-    </row>
-    <row r="45" ht="24" customHeight="1">
-      <c r="A45" s="3" t="inlineStr">
+    <row r="51" ht="24" customHeight="1">
+      <c r="A51" t="inlineStr"/>
+    </row>
+    <row r="52" ht="24" customHeight="1">
+      <c r="A52" t="inlineStr">
         <is>
           <t>base_probs = softmax(logits, 1.0)</t>
         </is>
       </c>
     </row>
-    <row r="46" ht="24" customHeight="1">
-      <c r="A46" s="3" t="inlineStr">
+    <row r="53" ht="24" customHeight="1">
+      <c r="A53" t="inlineStr">
         <is>
           <t>base_order = np.argsort(-base_probs)</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="24" customHeight="1">
-      <c r="A47" s="3" t="inlineStr">
+    <row r="54" ht="24" customHeight="1">
+      <c r="A54" t="inlineStr">
         <is>
           <t>greedy_token = vocab[int(base_order[0])]</t>
         </is>
       </c>
     </row>
-    <row r="48" ht="24" customHeight="1">
-      <c r="A48" s="3" t="inlineStr"/>
-    </row>
-    <row r="49" ht="24" customHeight="1">
-      <c r="A49" s="3" t="inlineStr">
+    <row r="55" ht="24" customHeight="1">
+      <c r="A55" t="inlineStr"/>
+    </row>
+    <row r="56" ht="24" customHeight="1">
+      <c r="A56" t="inlineStr">
         <is>
           <t>top_indices = base_order[:top_k]</t>
         </is>
       </c>
     </row>
-    <row r="50" ht="24" customHeight="1">
-      <c r="A50" s="3" t="inlineStr">
+    <row r="57" ht="24" customHeight="1">
+      <c r="A57" t="inlineStr">
         <is>
           <t>top_probs = base_probs[top_indices] / base_probs[top_indices].sum()</t>
         </is>
       </c>
     </row>
-    <row r="51" ht="24" customHeight="1">
-      <c r="A51" s="3" t="inlineStr">
+    <row r="58" ht="24" customHeight="1">
+      <c r="A58" t="inlineStr">
         <is>
           <t>top_k_rows = []</t>
         </is>
       </c>
     </row>
-    <row r="52" ht="24" customHeight="1">
-      <c r="A52" s="3" t="inlineStr">
+    <row r="59" ht="24" customHeight="1">
+      <c r="A59" t="inlineStr">
         <is>
           <t>for rank, (idx, adjusted_prob) in enumerate(zip(top_indices, top_probs), start=1):</t>
         </is>
       </c>
     </row>
-    <row r="53" ht="24" customHeight="1">
-      <c r="A53" s="3" t="inlineStr">
+    <row r="60" ht="24" customHeight="1">
+      <c r="A60" t="inlineStr">
         <is>
           <t xml:space="preserve">    top_k_rows.append({</t>
         </is>
       </c>
     </row>
-    <row r="54" ht="24" customHeight="1">
-      <c r="A54" s="3" t="inlineStr">
+    <row r="61" ht="24" customHeight="1">
+      <c r="A61" t="inlineStr">
         <is>
           <t xml:space="preserve">        "rank": rank,</t>
         </is>
       </c>
     </row>
-    <row r="55" ht="24" customHeight="1">
-      <c r="A55" s="3" t="inlineStr">
+    <row r="62" ht="24" customHeight="1">
+      <c r="A62" t="inlineStr">
         <is>
           <t xml:space="preserve">        "candidate_token": vocab[int(idx)],</t>
         </is>
       </c>
     </row>
-    <row r="56" ht="24" customHeight="1">
-      <c r="A56" s="3" t="inlineStr">
+    <row r="63" ht="24" customHeight="1">
+      <c r="A63" t="inlineStr">
         <is>
           <t xml:space="preserve">        "logit": round(float(logits[idx]), 4),</t>
         </is>
       </c>
     </row>
-    <row r="57" ht="24" customHeight="1">
-      <c r="A57" s="3" t="inlineStr">
+    <row r="64" ht="24" customHeight="1">
+      <c r="A64" t="inlineStr">
         <is>
           <t xml:space="preserve">        "original_probability": round(float(base_probs[idx]), 4),</t>
         </is>
       </c>
     </row>
-    <row r="58" ht="24" customHeight="1">
-      <c r="A58" s="3" t="inlineStr">
+    <row r="65" ht="24" customHeight="1">
+      <c r="A65" t="inlineStr">
         <is>
           <t xml:space="preserve">        "top_k_probability": round(float(adjusted_prob), 4),</t>
         </is>
       </c>
     </row>
-    <row r="59" ht="24" customHeight="1">
-      <c r="A59" s="3" t="inlineStr">
+    <row r="66" ht="24" customHeight="1">
+      <c r="A66" t="inlineStr">
         <is>
           <t xml:space="preserve">    })</t>
         </is>
       </c>
     </row>
-    <row r="60" ht="24" customHeight="1">
-      <c r="A60" s="3" t="inlineStr"/>
-    </row>
-    <row r="61" ht="24" customHeight="1">
-      <c r="A61" s="3" t="inlineStr">
+    <row r="67" ht="24" customHeight="1">
+      <c r="A67" t="inlineStr"/>
+    </row>
+    <row r="68" ht="24" customHeight="1">
+      <c r="A68" t="inlineStr">
         <is>
           <t>sample_rows = []</t>
         </is>
       </c>
     </row>
-    <row r="62" ht="24" customHeight="1">
-      <c r="A62" s="3" t="inlineStr">
+    <row r="69" ht="24" customHeight="1">
+      <c r="A69" t="inlineStr">
         <is>
           <t>for seed in seeds:</t>
         </is>
       </c>
     </row>
-    <row r="63" ht="24" customHeight="1">
-      <c r="A63" s="3" t="inlineStr">
+    <row r="70" ht="24" customHeight="1">
+      <c r="A70" t="inlineStr">
         <is>
           <t xml:space="preserve">    token, r = sample_from_probs(vocab, base_probs, seed)</t>
         </is>
       </c>
     </row>
-    <row r="64" ht="24" customHeight="1">
-      <c r="A64" s="3" t="inlineStr">
+    <row r="71" ht="24" customHeight="1">
+      <c r="A71" t="inlineStr">
         <is>
           <t xml:space="preserve">    sample_rows.append({</t>
         </is>
       </c>
     </row>
-    <row r="65" ht="24" customHeight="1">
-      <c r="A65" s="3" t="inlineStr">
+    <row r="72" ht="24" customHeight="1">
+      <c r="A72" t="inlineStr">
         <is>
           <t xml:space="preserve">        "seed": seed,</t>
         </is>
       </c>
     </row>
-    <row r="66" ht="24" customHeight="1">
-      <c r="A66" s="3" t="inlineStr">
+    <row r="73" ht="24" customHeight="1">
+      <c r="A73" t="inlineStr">
         <is>
           <t xml:space="preserve">        "random_value": round(r, 4),</t>
         </is>
       </c>
     </row>
-    <row r="67" ht="24" customHeight="1">
-      <c r="A67" s="3" t="inlineStr">
+    <row r="74" ht="24" customHeight="1">
+      <c r="A74" t="inlineStr">
         <is>
           <t xml:space="preserve">        "sampled_token": token,</t>
         </is>
       </c>
     </row>
-    <row r="68" ht="24" customHeight="1">
-      <c r="A68" s="3" t="inlineStr">
+    <row r="75" ht="24" customHeight="1">
+      <c r="A75" t="inlineStr">
         <is>
           <t xml:space="preserve">        "note": "同じ確率でも乱数が違うと選ばれるtokenが変わる",</t>
         </is>
       </c>
     </row>
-    <row r="69" ht="24" customHeight="1">
-      <c r="A69" s="3" t="inlineStr">
+    <row r="76" ht="24" customHeight="1">
+      <c r="A76" t="inlineStr">
         <is>
           <t xml:space="preserve">    })</t>
         </is>
       </c>
     </row>
-    <row r="70" ht="24" customHeight="1">
-      <c r="A70" s="3" t="inlineStr"/>
-    </row>
-    <row r="71" ht="24" customHeight="1">
-      <c r="A71" s="3" t="inlineStr">
+    <row r="77" ht="24" customHeight="1">
+      <c r="A77" t="inlineStr"/>
+    </row>
+    <row r="78" ht="24" customHeight="1">
+      <c r="A78" t="inlineStr">
         <is>
           <t>score_df = pd.DataFrame(score_rows)</t>
         </is>
       </c>
     </row>
-    <row r="72" ht="24" customHeight="1">
-      <c r="A72" s="3" t="inlineStr">
+    <row r="79" ht="24" customHeight="1">
+      <c r="A79" t="inlineStr">
         <is>
           <t>temperature_df = pd.DataFrame(temperature_rows)</t>
         </is>
       </c>
     </row>
-    <row r="73" ht="24" customHeight="1">
-      <c r="A73" s="3" t="inlineStr">
+    <row r="80" ht="24" customHeight="1">
+      <c r="A80" t="inlineStr">
         <is>
           <t>top_k_df = pd.DataFrame(top_k_rows)</t>
         </is>
       </c>
     </row>
-    <row r="74" ht="24" customHeight="1">
-      <c r="A74" s="3" t="inlineStr">
+    <row r="81" ht="24" customHeight="1">
+      <c r="A81" t="inlineStr">
         <is>
           <t>sample_df = pd.DataFrame(sample_rows)</t>
         </is>
       </c>
     </row>
-    <row r="75" ht="24" customHeight="1">
-      <c r="A75" s="3" t="inlineStr">
+    <row r="82" ht="24" customHeight="1">
+      <c r="A82" t="inlineStr">
         <is>
           <t>summary_df = pd.DataFrame([</t>
         </is>
       </c>
     </row>
-    <row r="76" ht="24" customHeight="1">
-      <c r="A76" s="3" t="inlineStr">
+    <row r="83" ht="24" customHeight="1">
+      <c r="A83" t="inlineStr">
         <is>
           <t xml:space="preserve">    {"mode": "greedy", "selected_token": greedy_token, "rule": "probabilityが最大のtokenを選ぶ"},</t>
         </is>
       </c>
     </row>
-    <row r="77" ht="24" customHeight="1">
-      <c r="A77" s="3" t="inlineStr">
+    <row r="84" ht="24" customHeight="1">
+      <c r="A84" t="inlineStr">
         <is>
           <t xml:space="preserve">    {"mode": "sampling", "selected_token": sample_df.loc[0, "sampled_token"], "rule": "probabilityに沿って乱数で選ぶ"},</t>
         </is>
       </c>
     </row>
-    <row r="78" ht="24" customHeight="1">
-      <c r="A78" s="3" t="inlineStr">
+    <row r="85" ht="24" customHeight="1">
+      <c r="A85" t="inlineStr">
         <is>
           <t xml:space="preserve">    {"mode": "top_k", "selected_token": top_k_df.loc[0, "candidate_token"], "rule": f"上位{top_k}件だけに絞って選ぶ"},</t>
         </is>
       </c>
     </row>
-    <row r="79" ht="24" customHeight="1">
-      <c r="A79" s="3" t="inlineStr">
+    <row r="86" ht="24" customHeight="1">
+      <c r="A86" t="inlineStr">
         <is>
           <t>])</t>
         </is>
       </c>
     </row>
-    <row r="80" ht="24" customHeight="1">
-      <c r="A80" s="3" t="inlineStr"/>
-    </row>
-    <row r="81" ht="24" customHeight="1">
-      <c r="A81" s="3" t="inlineStr">
+    <row r="87" ht="24" customHeight="1">
+      <c r="A87" t="inlineStr"/>
+    </row>
+    <row r="88" ht="24" customHeight="1">
+      <c r="A88" t="inlineStr">
         <is>
           <t># Python in Excelで最後に表示したい表を選びます。</t>
         </is>
       </c>
     </row>
-    <row r="82" ht="24" customHeight="1">
-      <c r="A82" s="3" t="inlineStr">
+    <row r="89">
+      <c r="A89" t="inlineStr">
         <is>
           <t>result_df = score_df</t>
         </is>
       </c>
     </row>
-    <row r="83" ht="24" customHeight="1">
-      <c r="A83" s="3" t="inlineStr">
+    <row r="90">
+      <c r="A90" t="inlineStr">
         <is>
           <t># result_df = temperature_df</t>
         </is>
       </c>
     </row>
-    <row r="84" ht="24" customHeight="1">
-      <c r="A84" s="3" t="inlineStr">
+    <row r="91">
+      <c r="A91" t="inlineStr">
         <is>
           <t># result_df = top_k_df</t>
         </is>
       </c>
     </row>
-    <row r="85" ht="24" customHeight="1">
-      <c r="A85" s="3" t="inlineStr">
+    <row r="92">
+      <c r="A92" t="inlineStr">
         <is>
           <t># result_df = sample_df</t>
         </is>
       </c>
     </row>
-    <row r="86" ht="24" customHeight="1">
-      <c r="A86" s="3" t="inlineStr">
+    <row r="93">
+      <c r="A93" t="inlineStr">
         <is>
           <t># result_df = summary_df</t>
         </is>
       </c>
     </row>
-    <row r="87" ht="24" customHeight="1">
-      <c r="A87" s="3" t="inlineStr"/>
-    </row>
-    <row r="88" ht="24" customHeight="1">
-      <c r="A88" s="3" t="inlineStr">
+    <row r="94">
+      <c r="A94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
         <is>
           <t>result_df</t>
         </is>

--- a/第7回_Softmax_Generation/excel_softmax_generation_demo.xlsx
+++ b/第7回_Softmax_Generation/excel_softmax_generation_demo.xlsx
@@ -131,7 +131,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -166,6 +166,12 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -689,7 +695,7 @@
       <c r="B3" s="3" t="n"/>
     </row>
     <row r="4" ht="24" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="14" t="inlineStr">
         <is>
           <t>よくある確認点</t>
         </is>
@@ -805,7 +811,7 @@
       <c r="C3" s="3" t="n"/>
     </row>
     <row r="4" ht="24" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="14" t="inlineStr">
         <is>
           <t>全10回ロードマップ</t>
         </is>
@@ -1059,7 +1065,7 @@
       <c r="J2" s="3" t="n"/>
     </row>
     <row r="3" ht="24" customHeight="1">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>第6回のBlock Output後に語彙ごとのlogitが得られたと仮定し、Softmaxと選択方法だけを小さく確認します。</t>
         </is>
@@ -1087,7 +1093,7 @@
       <c r="J4" s="3" t="n"/>
     </row>
     <row r="5" ht="24" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="14" t="inlineStr">
         <is>
           <t>文脈token</t>
         </is>
@@ -1095,7 +1101,7 @@
       <c r="B5" s="2" t="n"/>
       <c r="C5" s="3" t="n"/>
       <c r="D5" s="3" t="n"/>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="E5" s="14" t="inlineStr">
         <is>
           <t>候補tokenとlogit</t>
         </is>
@@ -1279,7 +1285,7 @@
       <c r="J13" s="3" t="n"/>
     </row>
     <row r="14" ht="24" customHeight="1">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="A14" s="14" t="inlineStr">
         <is>
           <t>生成設定</t>
         </is>
@@ -1442,7 +1448,7 @@
       <c r="H2" s="3" t="n"/>
     </row>
     <row r="3" ht="24" customHeight="1">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>logitは確率そのものではありません。Softmaxで合計1の確率に変換してから候補を選びます。</t>
         </is>
@@ -1466,7 +1472,7 @@
       <c r="H4" s="3" t="n"/>
     </row>
     <row r="5" ht="24" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="14" t="inlineStr">
         <is>
           <t>temperature=1.0 の確率表</t>
         </is>
@@ -1695,7 +1701,7 @@
       <c r="H2" s="3" t="n"/>
     </row>
     <row r="3" ht="24" customHeight="1">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>temperatureを下げると上位候補に寄り、上げると候補間の差がなだらかになります。</t>
         </is>
@@ -1719,7 +1725,7 @@
       <c r="H4" s="3" t="n"/>
     </row>
     <row r="5" ht="24" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="14" t="inlineStr">
         <is>
           <t>temperature比較</t>
         </is>
@@ -2255,7 +2261,7 @@
       <c r="I2" s="3" t="n"/>
     </row>
     <row r="3" ht="24" customHeight="1">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>確率表が同じでも、greedy、sampling、top-kでは選ばれ方が変わります。</t>
         </is>
@@ -2281,7 +2287,7 @@
       <c r="I4" s="3" t="n"/>
     </row>
     <row r="5" ht="24" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="14" t="inlineStr">
         <is>
           <t>選択方法</t>
         </is>
@@ -2399,7 +2405,7 @@
       <c r="I10" s="3" t="n"/>
     </row>
     <row r="11" ht="24" customHeight="1">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="14" t="inlineStr">
         <is>
           <t>top-kで残す候補</t>
         </is>
@@ -2568,7 +2574,7 @@
       <c r="H2" s="3" t="n"/>
     </row>
     <row r="3" ht="24" customHeight="1">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>samplingでは確率に沿って選ぶため、最大確率以外のtokenが選ばれることがあります。</t>
         </is>
@@ -2592,7 +2598,7 @@
       <c r="H4" s="3" t="n"/>
     </row>
     <row r="5" ht="24" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="14" t="inlineStr">
         <is>
           <t>sampling結果</t>
         </is>
@@ -2791,7 +2797,7 @@
       <c r="C3" s="3" t="n"/>
     </row>
     <row r="4" ht="24" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="14" t="inlineStr">
         <is>
           <t>生成フロー</t>
         </is>
@@ -2948,7 +2954,7 @@
       <c r="B3" s="3" t="n"/>
     </row>
     <row r="4" ht="24" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="14" t="inlineStr">
         <is>
           <t>実行手順</t>
         </is>
@@ -3042,7 +3048,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A95"/>
+  <dimension ref="A1:F95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="135" customWidth="1" min="1" max="1"/>
@@ -3082,9 +3088,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="24" customHeight="1">
-      <c r="A6" t="inlineStr"/>
-    </row>
+    <row r="6" ht="24" customHeight="1"/>
     <row r="7" ht="24" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
@@ -3106,9 +3110,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="24" customHeight="1">
-      <c r="A10" t="inlineStr"/>
-    </row>
+    <row r="10" ht="24" customHeight="1"/>
     <row r="11" ht="24" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
@@ -3165,9 +3167,7 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="24" customHeight="1">
-      <c r="A19" t="inlineStr"/>
-    </row>
+    <row r="19" ht="24" customHeight="1"/>
     <row r="20" ht="24" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
@@ -3203,9 +3203,7 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="24" customHeight="1">
-      <c r="A25" t="inlineStr"/>
-    </row>
+    <row r="25" ht="24" customHeight="1"/>
     <row r="26" ht="24" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
@@ -3255,9 +3253,7 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="24" customHeight="1">
-      <c r="A33" t="inlineStr"/>
-    </row>
+    <row r="33" ht="24" customHeight="1"/>
     <row r="34" ht="24" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
@@ -3377,9 +3373,7 @@
         </is>
       </c>
     </row>
-    <row r="51" ht="24" customHeight="1">
-      <c r="A51" t="inlineStr"/>
-    </row>
+    <row r="51" ht="24" customHeight="1"/>
     <row r="52" ht="24" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
@@ -3401,9 +3395,7 @@
         </is>
       </c>
     </row>
-    <row r="55" ht="24" customHeight="1">
-      <c r="A55" t="inlineStr"/>
-    </row>
+    <row r="55" ht="24" customHeight="1"/>
     <row r="56" ht="24" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
@@ -3481,9 +3473,7 @@
         </is>
       </c>
     </row>
-    <row r="67" ht="24" customHeight="1">
-      <c r="A67" t="inlineStr"/>
-    </row>
+    <row r="67" ht="24" customHeight="1"/>
     <row r="68" ht="24" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
@@ -3547,9 +3537,7 @@
         </is>
       </c>
     </row>
-    <row r="77" ht="24" customHeight="1">
-      <c r="A77" t="inlineStr"/>
-    </row>
+    <row r="77" ht="24" customHeight="1"/>
     <row r="78" ht="24" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
@@ -3613,9 +3601,7 @@
         </is>
       </c>
     </row>
-    <row r="87" ht="24" customHeight="1">
-      <c r="A87" t="inlineStr"/>
-    </row>
+    <row r="87" ht="24" customHeight="1"/>
     <row r="88" ht="24" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
@@ -3658,9 +3644,7 @@
         </is>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" t="inlineStr"/>
-    </row>
+    <row r="94"/>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
